--- a/Team-Data/2007-08/4-12-2007-08.xlsx
+++ b/Team-Data/2007-08/4-12-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="n">
         <v>37</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>0.463</v>
+        <v>0.468</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
@@ -691,67 +758,67 @@
         <v>13.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.357</v>
+        <v>0.36</v>
       </c>
       <c r="O2" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="P2" t="n">
         <v>27.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R2" t="n">
         <v>12.3</v>
       </c>
       <c r="S2" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T2" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U2" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V2" t="n">
         <v>14.9</v>
       </c>
       <c r="W2" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X2" t="n">
         <v>5.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z2" t="n">
         <v>20.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI2" t="n">
         <v>21</v>
@@ -766,16 +833,16 @@
         <v>27</v>
       </c>
       <c r="AM2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
         <v>5</v>
       </c>
       <c r="AP2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ2" t="n">
         <v>7</v>
@@ -784,7 +851,7 @@
         <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
         <v>11</v>
@@ -814,7 +881,7 @@
         <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F3" t="n">
         <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
@@ -870,19 +937,19 @@
         <v>7.3</v>
       </c>
       <c r="M3" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N3" t="n">
         <v>0.379</v>
       </c>
       <c r="O3" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="P3" t="n">
         <v>26.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="R3" t="n">
         <v>10.1</v>
@@ -897,7 +964,7 @@
         <v>22.5</v>
       </c>
       <c r="V3" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W3" t="n">
         <v>8.5</v>
@@ -909,7 +976,7 @@
         <v>4.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AA3" t="n">
         <v>22.2</v>
@@ -921,7 +988,7 @@
         <v>10.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -945,13 +1012,13 @@
         <v>4</v>
       </c>
       <c r="AL3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM3" t="n">
         <v>12</v>
       </c>
       <c r="AN3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="n">
         <v>8</v>
@@ -963,13 +1030,13 @@
         <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS3" t="n">
         <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
         <v>8</v>
@@ -981,10 +1048,10 @@
         <v>5</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ3" t="n">
         <v>25</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
         <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>0.388</v>
+        <v>0.38</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
@@ -1043,7 +1110,7 @@
         <v>36</v>
       </c>
       <c r="J4" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="K4" t="n">
         <v>0.451</v>
@@ -1052,28 +1119,28 @@
         <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="N4" t="n">
         <v>0.367</v>
       </c>
       <c r="O4" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P4" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.711</v>
+        <v>0.71</v>
       </c>
       <c r="R4" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="S4" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T4" t="n">
-        <v>40.6</v>
+        <v>40.3</v>
       </c>
       <c r="U4" t="n">
         <v>21.2</v>
@@ -1085,28 +1152,28 @@
         <v>7.5</v>
       </c>
       <c r="X4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y4" t="n">
         <v>5.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.5</v>
+        <v>-4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
         <v>23</v>
@@ -1115,7 +1182,7 @@
         <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
         <v>25</v>
@@ -1124,10 +1191,10 @@
         <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM4" t="n">
         <v>15</v>
@@ -1148,19 +1215,19 @@
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
         <v>26</v>
       </c>
       <c r="AU4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AV4" t="n">
         <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1172,10 +1239,10 @@
         <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1327,7 +1394,7 @@
         <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS5" t="n">
         <v>18</v>
@@ -1357,7 +1424,7 @@
         <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1485,7 +1552,7 @@
         <v>24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK6" t="n">
         <v>28</v>
@@ -1497,13 +1564,13 @@
         <v>13</v>
       </c>
       <c r="AN6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO6" t="n">
         <v>21</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
@@ -1530,7 +1597,7 @@
         <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ6" t="n">
         <v>16</v>
@@ -1542,7 +1609,7 @@
         <v>18</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -1571,31 +1638,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" t="n">
         <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>0.625</v>
+        <v>0.633</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J7" t="n">
         <v>79.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M7" t="n">
         <v>16.9</v>
@@ -1604,7 +1671,7 @@
         <v>0.352</v>
       </c>
       <c r="O7" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="P7" t="n">
         <v>25.4</v>
@@ -1616,13 +1683,13 @@
         <v>10.7</v>
       </c>
       <c r="S7" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T7" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="U7" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="V7" t="n">
         <v>12.8</v>
@@ -1643,13 +1710,13 @@
         <v>21.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.4</v>
+        <v>100.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
@@ -1661,7 +1728,7 @@
         <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
@@ -1670,7 +1737,7 @@
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>20</v>
@@ -1685,13 +1752,13 @@
         <v>7</v>
       </c>
       <c r="AP7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
         <v>7</v>
@@ -1700,7 +1767,7 @@
         <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV7" t="n">
         <v>5</v>
@@ -1709,7 +1776,7 @@
         <v>29</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" t="n">
         <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>0.608</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,28 +1838,28 @@
         <v>40.3</v>
       </c>
       <c r="J8" t="n">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0.47</v>
       </c>
       <c r="L8" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O8" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="P8" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="R8" t="n">
         <v>11.3</v>
@@ -1801,16 +1868,16 @@
         <v>32.7</v>
       </c>
       <c r="T8" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U8" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="V8" t="n">
         <v>14.7</v>
       </c>
       <c r="W8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>6.6</v>
@@ -1819,19 +1886,19 @@
         <v>4.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA8" t="n">
         <v>23.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>110.5</v>
+        <v>110.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1843,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1855,7 +1922,7 @@
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
@@ -1870,16 +1937,16 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU8" t="n">
         <v>3</v>
@@ -1894,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ8" t="n">
         <v>17</v>
@@ -1903,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="BB8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC8" t="n">
         <v>11</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2037,7 +2104,7 @@
         <v>13</v>
       </c>
       <c r="AL9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM9" t="n">
         <v>22</v>
@@ -2049,7 +2116,7 @@
         <v>19</v>
       </c>
       <c r="AP9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ9" t="n">
         <v>14</v>
@@ -2061,7 +2128,7 @@
         <v>25</v>
       </c>
       <c r="AT9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
         <v>9</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
         <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2150,25 +2217,25 @@
         <v>0.348</v>
       </c>
       <c r="O10" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P10" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R10" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S10" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T10" t="n">
         <v>43.1</v>
       </c>
       <c r="U10" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V10" t="n">
         <v>13.3</v>
@@ -2180,34 +2247,34 @@
         <v>4.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA10" t="n">
         <v>21.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>110.9</v>
+        <v>110.7</v>
       </c>
       <c r="AC10" t="n">
         <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2231,10 +2298,10 @@
         <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR10" t="n">
         <v>5</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -2377,13 +2444,13 @@
         <v>5</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>5</v>
       </c>
       <c r="AF11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG11" t="n">
         <v>5</v>
@@ -2407,7 +2474,7 @@
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO11" t="n">
         <v>28</v>
@@ -2419,7 +2486,7 @@
         <v>26</v>
       </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
         <v>6</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" t="n">
         <v>35</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>0.438</v>
+        <v>0.443</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2508,10 +2575,10 @@
         <v>9.1</v>
       </c>
       <c r="M12" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O12" t="n">
         <v>18.9</v>
@@ -2520,7 +2587,7 @@
         <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R12" t="n">
         <v>11.1</v>
@@ -2532,13 +2599,13 @@
         <v>43.2</v>
       </c>
       <c r="U12" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V12" t="n">
         <v>15.1</v>
       </c>
       <c r="W12" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X12" t="n">
         <v>5</v>
@@ -2556,10 +2623,10 @@
         <v>103.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2580,7 +2647,7 @@
         <v>4</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2598,7 +2665,7 @@
         <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2619,7 +2686,7 @@
         <v>11</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
@@ -2634,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -2663,58 +2730,58 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" t="n">
         <v>23</v>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>0.288</v>
+        <v>0.291</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="J13" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>0.438</v>
       </c>
       <c r="L13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="M13" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="N13" t="n">
         <v>0.323</v>
       </c>
       <c r="O13" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="P13" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T13" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="U13" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="n">
         <v>14.4</v>
@@ -2735,13 +2802,13 @@
         <v>21.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="AC13" t="n">
         <v>-7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,13 +2820,13 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
@@ -2792,7 +2859,7 @@
         <v>29</v>
       </c>
       <c r="AU13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV13" t="n">
         <v>12</v>
@@ -2801,13 +2868,13 @@
         <v>19</v>
       </c>
       <c r="AX13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY13" t="n">
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
         <v>10</v>
@@ -2816,7 +2883,7 @@
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -2929,13 +2996,13 @@
         <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -2950,13 +3017,13 @@
         <v>5</v>
       </c>
       <c r="AM14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN14" t="n">
         <v>7</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
         <v>5</v>
@@ -2971,7 +3038,7 @@
         <v>1</v>
       </c>
       <c r="AT14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" t="n">
         <v>22</v>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>0.275</v>
+        <v>0.278</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
@@ -3045,10 +3112,10 @@
         <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L15" t="n">
         <v>7.5</v>
@@ -3060,16 +3127,16 @@
         <v>0.352</v>
       </c>
       <c r="O15" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P15" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.725</v>
+        <v>0.728</v>
       </c>
       <c r="R15" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S15" t="n">
         <v>31.2</v>
@@ -3081,10 +3148,10 @@
         <v>19</v>
       </c>
       <c r="V15" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W15" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X15" t="n">
         <v>4.7</v>
@@ -3099,52 +3166,52 @@
         <v>22.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.7</v>
+        <v>100.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6</v>
+        <v>-5.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
       </c>
       <c r="AH15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>14</v>
       </c>
-      <c r="AI15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>13</v>
-      </c>
       <c r="AK15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL15" t="n">
         <v>7</v>
       </c>
       <c r="AM15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
@@ -3153,7 +3220,7 @@
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU15" t="n">
         <v>29</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3326,7 +3393,7 @@
         <v>23</v>
       </c>
       <c r="AQ16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" t="n">
         <v>26</v>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>0.325</v>
+        <v>0.329</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3409,49 +3476,49 @@
         <v>36.7</v>
       </c>
       <c r="J17" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L17" t="n">
         <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O17" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="P17" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="R17" t="n">
         <v>12.9</v>
       </c>
       <c r="S17" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U17" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V17" t="n">
         <v>14.7</v>
       </c>
       <c r="W17" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y17" t="n">
         <v>5</v>
@@ -3466,10 +3533,10 @@
         <v>96.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3481,13 +3548,13 @@
         <v>24</v>
       </c>
       <c r="AH17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI17" t="n">
         <v>17</v>
       </c>
       <c r="AJ17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK17" t="n">
         <v>21</v>
@@ -3499,19 +3566,19 @@
         <v>23</v>
       </c>
       <c r="AN17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO17" t="n">
         <v>22</v>
       </c>
       <c r="AP17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS17" t="n">
         <v>29</v>
@@ -3520,25 +3587,25 @@
         <v>17</v>
       </c>
       <c r="AU17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV17" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AW17" t="n">
         <v>21</v>
       </c>
       <c r="AX17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
         <v>19</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>24</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -3573,25 +3640,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F18" t="n">
         <v>59</v>
       </c>
       <c r="G18" t="n">
-        <v>0.263</v>
+        <v>0.253</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
       </c>
       <c r="I18" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J18" t="n">
-        <v>82.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="K18" t="n">
         <v>0.451</v>
@@ -3609,19 +3676,19 @@
         <v>15.2</v>
       </c>
       <c r="P18" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="Q18" t="n">
         <v>0.738</v>
       </c>
       <c r="R18" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S18" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T18" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U18" t="n">
         <v>19.8</v>
@@ -3633,7 +3700,7 @@
         <v>7.5</v>
       </c>
       <c r="X18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y18" t="n">
         <v>5.7</v>
@@ -3645,13 +3712,13 @@
         <v>17.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>95.3</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6.9</v>
+        <v>-7.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
@@ -3666,13 +3733,13 @@
         <v>29</v>
       </c>
       <c r="AI18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AK18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AL18" t="n">
         <v>25</v>
@@ -3699,7 +3766,7 @@
         <v>24</v>
       </c>
       <c r="AT18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU18" t="n">
         <v>26</v>
@@ -3708,7 +3775,7 @@
         <v>18</v>
       </c>
       <c r="AW18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3723,10 +3790,10 @@
         <v>30</v>
       </c>
       <c r="BB18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F19" t="n">
         <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>0.413</v>
+        <v>0.405</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="J19" t="n">
         <v>78.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.443</v>
+        <v>0.441</v>
       </c>
       <c r="L19" t="n">
         <v>6</v>
@@ -3785,28 +3852,28 @@
         <v>17.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O19" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P19" t="n">
-        <v>27.1</v>
+        <v>27.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.735</v>
+        <v>0.733</v>
       </c>
       <c r="R19" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S19" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T19" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U19" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V19" t="n">
         <v>15</v>
@@ -3818,22 +3885,22 @@
         <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z19" t="n">
         <v>22.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.59999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.1</v>
+        <v>-5.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>21</v>
@@ -3845,22 +3912,22 @@
         <v>21</v>
       </c>
       <c r="AH19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI19" t="n">
         <v>28</v>
       </c>
       <c r="AJ19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK19" t="n">
         <v>26</v>
       </c>
-      <c r="AK19" t="n">
-        <v>25</v>
-      </c>
       <c r="AL19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM19" t="n">
         <v>18</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>17</v>
       </c>
       <c r="AN19" t="n">
         <v>24</v>
@@ -3869,10 +3936,10 @@
         <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR19" t="n">
         <v>15</v>
@@ -3881,7 +3948,7 @@
         <v>13</v>
       </c>
       <c r="AT19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU19" t="n">
         <v>6</v>
@@ -3890,13 +3957,13 @@
         <v>25</v>
       </c>
       <c r="AW19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX19" t="n">
         <v>16</v>
       </c>
       <c r="AY19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
         <v>26</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -3937,43 +4004,43 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" t="n">
         <v>55</v>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.696</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J20" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L20" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M20" t="n">
         <v>19.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.39</v>
+        <v>0.392</v>
       </c>
       <c r="O20" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P20" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="Q20" t="n">
         <v>0.767</v>
@@ -3985,19 +4052,19 @@
         <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U20" t="n">
         <v>21.8</v>
       </c>
       <c r="V20" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="W20" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X20" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y20" t="n">
         <v>4.1</v>
@@ -4006,16 +4073,16 @@
         <v>18.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.7</v>
+        <v>100.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>3</v>
@@ -4027,16 +4094,16 @@
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
       </c>
       <c r="AJ20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK20" t="n">
         <v>8</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>9</v>
       </c>
       <c r="AL20" t="n">
         <v>6</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -4203,10 +4270,10 @@
         <v>25</v>
       </c>
       <c r="AF21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH21" t="n">
         <v>3</v>
@@ -4215,7 +4282,7 @@
         <v>22</v>
       </c>
       <c r="AJ21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK21" t="n">
         <v>27</v>
@@ -4233,7 +4300,7 @@
         <v>18</v>
       </c>
       <c r="AP21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ21" t="n">
         <v>25</v>
@@ -4242,7 +4309,7 @@
         <v>6</v>
       </c>
       <c r="AS21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -4254,7 +4321,7 @@
         <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,13 +4330,13 @@
         <v>25</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
         <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -4379,13 +4446,13 @@
         <v>5</v>
       </c>
       <c r="AD22" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>10</v>
       </c>
       <c r="AF22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG22" t="n">
         <v>10</v>
@@ -4394,7 +4461,7 @@
         <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
         <v>27</v>
@@ -4415,7 +4482,7 @@
         <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ22" t="n">
         <v>27</v>
@@ -4424,10 +4491,10 @@
         <v>28</v>
       </c>
       <c r="AS22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU22" t="n">
         <v>22</v>
@@ -4442,7 +4509,7 @@
         <v>25</v>
       </c>
       <c r="AY22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ22" t="n">
         <v>14</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" t="n">
         <v>40</v>
       </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5</v>
+        <v>0.506</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4513,13 +4580,13 @@
         <v>11.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.315</v>
+        <v>0.313</v>
       </c>
       <c r="O23" t="n">
         <v>18.6</v>
       </c>
       <c r="P23" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="Q23" t="n">
         <v>0.707</v>
@@ -4531,7 +4598,7 @@
         <v>29</v>
       </c>
       <c r="T23" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U23" t="n">
         <v>20.4</v>
@@ -4549,7 +4616,7 @@
         <v>5</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA23" t="n">
         <v>20.9</v>
@@ -4558,25 +4625,25 @@
         <v>96.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>15</v>
       </c>
       <c r="AF23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH23" t="n">
         <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ23" t="n">
         <v>17</v>
@@ -4588,13 +4655,13 @@
         <v>30</v>
       </c>
       <c r="AM23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AN23" t="n">
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP23" t="n">
         <v>10</v>
@@ -4615,13 +4682,13 @@
         <v>23</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
         <v>4</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY23" t="n">
         <v>20</v>
@@ -4633,7 +4700,7 @@
         <v>18</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -4755,13 +4822,13 @@
         <v>7</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK24" t="n">
         <v>1</v>
@@ -4791,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4812,7 +4879,7 @@
         <v>9</v>
       </c>
       <c r="BA24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
         <v>3</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -4847,37 +4914,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F25" t="n">
         <v>40</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>0.494</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J25" t="n">
         <v>79.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L25" t="n">
         <v>6.5</v>
       </c>
       <c r="M25" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="O25" t="n">
         <v>17.3</v>
@@ -4889,52 +4956,52 @@
         <v>0.769</v>
       </c>
       <c r="R25" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S25" t="n">
         <v>29.7</v>
       </c>
       <c r="T25" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U25" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V25" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W25" t="n">
         <v>5.5</v>
       </c>
       <c r="X25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y25" t="n">
         <v>3.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="n">
         <v>20.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.2</v>
+        <v>95</v>
       </c>
       <c r="AC25" t="n">
         <v>-1.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH25" t="n">
         <v>1</v>
@@ -4943,16 +5010,16 @@
         <v>27</v>
       </c>
       <c r="AJ25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK25" t="n">
         <v>20</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN25" t="n">
         <v>8</v>
@@ -4964,7 +5031,7 @@
         <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR25" t="n">
         <v>18</v>
@@ -4973,7 +5040,7 @@
         <v>22</v>
       </c>
       <c r="AT25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU25" t="n">
         <v>19</v>
@@ -4994,7 +5061,7 @@
         <v>8</v>
       </c>
       <c r="BA25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F26" t="n">
         <v>42</v>
       </c>
       <c r="G26" t="n">
-        <v>0.475</v>
+        <v>0.468</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5053,31 +5120,31 @@
         <v>0.464</v>
       </c>
       <c r="L26" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M26" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O26" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="P26" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="R26" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S26" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="T26" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U26" t="n">
         <v>19.1</v>
@@ -5092,22 +5159,22 @@
         <v>4.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AA26" t="n">
         <v>23.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.6</v>
+        <v>102.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,7 +5186,7 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
         <v>14</v>
@@ -5152,7 +5219,7 @@
         <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
         <v>28</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>4.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>5</v>
       </c>
       <c r="AF27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG27" t="n">
         <v>5</v>
@@ -5310,10 +5377,10 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM27" t="n">
         <v>9</v>
@@ -5337,22 +5404,22 @@
         <v>9</v>
       </c>
       <c r="AT27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV27" t="n">
         <v>4</v>
       </c>
       <c r="AW27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX27" t="n">
         <v>24</v>
       </c>
       <c r="AY27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ27" t="n">
         <v>2</v>
@@ -5361,7 +5428,7 @@
         <v>24</v>
       </c>
       <c r="BB27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC27" t="n">
         <v>9</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5550,7 @@
         <v>29</v>
       </c>
       <c r="AH28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5510,7 +5577,7 @@
         <v>24</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
         <v>11</v>
@@ -5522,7 +5589,7 @@
         <v>2</v>
       </c>
       <c r="AU28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV28" t="n">
         <v>30</v>
@@ -5531,7 +5598,7 @@
         <v>23</v>
       </c>
       <c r="AX28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY28" t="n">
         <v>26</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>15</v>
@@ -5713,7 +5780,7 @@
         <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F30" t="n">
         <v>27</v>
       </c>
       <c r="G30" t="n">
-        <v>0.663</v>
+        <v>0.658</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="J30" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.499</v>
+        <v>0.498</v>
       </c>
       <c r="L30" t="n">
         <v>5</v>
@@ -5787,13 +5854,13 @@
         <v>13.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.377</v>
+        <v>0.379</v>
       </c>
       <c r="O30" t="n">
         <v>21.3</v>
       </c>
       <c r="P30" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="Q30" t="n">
         <v>0.759</v>
@@ -5802,13 +5869,13 @@
         <v>11.5</v>
       </c>
       <c r="S30" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T30" t="n">
         <v>40.8</v>
       </c>
       <c r="U30" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="V30" t="n">
         <v>14.7</v>
@@ -5817,7 +5884,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y30" t="n">
         <v>5.2</v>
@@ -5829,22 +5896,22 @@
         <v>23.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>106.6</v>
+        <v>106.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF30" t="n">
         <v>7</v>
       </c>
       <c r="AG30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5865,13 +5932,13 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ30" t="n">
         <v>16</v>
@@ -5883,13 +5950,13 @@
         <v>26</v>
       </c>
       <c r="AT30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E31" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F31" t="n">
         <v>38</v>
       </c>
       <c r="G31" t="n">
-        <v>0.525</v>
+        <v>0.519</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
@@ -5957,19 +6024,19 @@
         <v>36.3</v>
       </c>
       <c r="J31" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L31" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M31" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.355</v>
+        <v>0.352</v>
       </c>
       <c r="O31" t="n">
         <v>19.2</v>
@@ -5978,19 +6045,19 @@
         <v>24.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="R31" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S31" t="n">
         <v>29.2</v>
       </c>
       <c r="T31" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U31" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="V31" t="n">
         <v>13.2</v>
@@ -5999,10 +6066,10 @@
         <v>7.8</v>
       </c>
       <c r="X31" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z31" t="n">
         <v>19.6</v>
@@ -6011,13 +6078,13 @@
         <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.8</v>
+        <v>98.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6041,13 +6108,13 @@
         <v>22</v>
       </c>
       <c r="AL31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM31" t="n">
         <v>10</v>
       </c>
       <c r="AN31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6059,7 +6126,7 @@
         <v>4</v>
       </c>
       <c r="AR31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS31" t="n">
         <v>27</v>
@@ -6077,22 +6144,22 @@
         <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
         <v>6</v>
       </c>
       <c r="BA31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB31" t="n">
         <v>14</v>
       </c>
       <c r="BC31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-12-2007-08</t>
+          <t>2008-04-12</t>
         </is>
       </c>
     </row>
